--- a/output/pdf_financials_xlsx/FAT.xlsx
+++ b/output/pdf_financials_xlsx/FAT.xlsx
@@ -2388,13 +2388,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>2.462047</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>3.280933</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>3.294831</v>
       </c>
     </row>
     <row r="93">
@@ -2879,16 +2879,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-4.368564</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-2.382193</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-1.967017</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.127153</v>
+        <v>-8.433138</v>
       </c>
     </row>
     <row r="119">
@@ -3924,7 +3924,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -4434,7 +4438,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -6466,7 +6474,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E91" s="5" t="n">
         <v>-4.368564</v>
       </c>

--- a/output/pdf_financials_xlsx/FAT.xlsx
+++ b/output/pdf_financials_xlsx/FAT.xlsx
@@ -1150,13 +1150,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.998262</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.005346</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>6.342205</v>
       </c>
     </row>
     <row r="35">
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.998262</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.005346</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.262376</v>
+        <v>7.604581</v>
       </c>
     </row>
     <row r="37">
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.339004</v>
+        <v>0.340742</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.128683</v>
+        <v>0.123337</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>5.305254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>0.065702</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>0.032851</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -3012,10 +3012,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>0.065702</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>0.032851</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6612,7 +6612,11 @@
           <t>Receipt of sublease payments</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E95" s="5" t="n">
         <v>0.065702</v>
       </c>
@@ -8356,7 +8360,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">

--- a/output/pdf_financials_xlsx/FAT.xlsx
+++ b/output/pdf_financials_xlsx/FAT.xlsx
@@ -555,13 +555,13 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.070379</v>
+        <v>0.824921</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.025209</v>
+        <v>0.833759</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.038235</v>
+        <v>1.210995</v>
       </c>
     </row>
     <row r="8">
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.535406</v>
+        <v>1.289948</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.461866</v>
+        <v>1.270416</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.576856</v>
+        <v>1.749616</v>
       </c>
     </row>
     <row r="11">
@@ -7598,7 +7598,11 @@
           <t>Private placements</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E124" s="5" t="n">
         <v>1.661807</v>
       </c>
@@ -7730,7 +7734,11 @@
           <t>Management and director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
